--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.8932638566003</v>
+        <v>2.907655376697549</v>
       </c>
       <c r="D2" t="n">
-        <v>18.71894702090809</v>
+        <v>3.041828890897564</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3931525288389359</v>
+        <v>0.06388728593632709</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3002447455328277</v>
+        <v>0.04878977114908456</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.67956891427817</v>
+        <v>3.035429948570203</v>
       </c>
       <c r="D3" t="n">
-        <v>19.31943651197374</v>
+        <v>3.139408433195733</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3931525288389359</v>
+        <v>0.06388728593632709</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3002447455328277</v>
+        <v>0.04878977114908456</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
